--- a/contenedores/airflow/mantenedores/parametros_generales.xlsx
+++ b/contenedores/airflow/mantenedores/parametros_generales.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/78ec6eafe1d282b6/Felipe/Projects/CMF/finReport/contenedores/airflow/mantenedores/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="11_F25DC773A252ABDACC104864C11848EE5ADE58EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{973359EA-8C19-44A3-A25E-E66F2FC82DF7}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="11_F25DC773A252ABDACC104864C11848EE5ADE58EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{706D93AE-B597-424D-9C2B-02CEE72B683F}"/>
   <bookViews>
-    <workbookView xWindow="13590" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="parametros_generales" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>cod</t>
   </si>
@@ -58,6 +58,24 @@
   </si>
   <si>
     <t>20251107</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Carga de interfaces en formato TXT</t>
+  </si>
+  <si>
+    <t>SI</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>Carga de interfaces en formato EXCEL .xlsx</t>
   </si>
 </sst>
 </file>
@@ -111,10 +129,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -380,15 +394,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="1"/>
-    <col min="2" max="2" width="28.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="8.85546875" style="1"/>
+    <col min="2" max="2" width="39.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -399,7 +413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -410,7 +424,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -421,7 +435,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -430,6 +444,28 @@
       </c>
       <c r="C4" s="1" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
